--- a/artfynd/A 51769-2022 artfynd.xlsx
+++ b/artfynd/A 51769-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51769-2022 artfynd.xlsx
+++ b/artfynd/A 51769-2022 artfynd.xlsx
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3418948</v>
+        <v>3006631</v>
       </c>
       <c r="B2" t="n">
-        <v>103264</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Humslid, Stormossen, Vrm</t>
+          <t>Ävjetjärnen, O om, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370313.8315618474</v>
+        <v>370368</v>
       </c>
       <c r="R2" t="n">
-        <v>6610133.670238215</v>
+        <v>6610094</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,29 +738,24 @@
           <t>Högerud</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>S-Arv-0813</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-11-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-11-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vuxen gallrad granskog med stort inslag av tall</t>
+          <t>ej räknad, noterad med 100 m noggrannhet vid 6613955-1324855</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,35 +767,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Värmland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Per Larsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Per Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>3017444</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370354.0920818726</v>
+        <v>370354</v>
       </c>
       <c r="R3" t="n">
-        <v>6610124.172766313</v>
+        <v>6610124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +859,9 @@
           <t>2004-11-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-11-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,54 +898,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104408640</v>
+        <v>3418948</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arvika, Vrm</t>
+          <t>Humslid, Stormossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>370368.2795000765</v>
+        <v>370314</v>
       </c>
       <c r="R4" t="n">
-        <v>6610094.305096432</v>
+        <v>6610134</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,22 +968,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2004-11-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2004-11-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>vuxen gallrad granskog med stort inslag av tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,15 +990,20 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>jenny klevmark</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>jenny klevmark</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
